--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC37959-E689-416B-9445-ACCC978E129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D8D8B6-DA67-4440-92A2-1F1D33CC6424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>project_name</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>פרויקט אישי - דשבורד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בנק יהב </t>
+  </si>
+  <si>
+    <t>מעבר על ליקויי אבטחה</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81840B73-A939-4138-9F05-60B93E3DBEB3}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -507,7 +513,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -527,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -536,6 +542,26 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46130</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC37959-E689-416B-9445-ACCC978E129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBF41A7-AD30-4743-B13B-8C7C01069974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>project_name</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>פרויקט אישי - דשבורד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בנק יהב </t>
+  </si>
+  <si>
+    <t>מעבר על ליקויי אבטחה</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81840B73-A939-4138-9F05-60B93E3DBEB3}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -507,7 +513,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -527,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -536,6 +542,26 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46131</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBF41A7-AD30-4743-B13B-8C7C01069974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347EC3FB-1B72-4243-9EBD-6BA1BE9F0BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>project_name</t>
   </si>
@@ -47,9 +47,6 @@
     <t>date</t>
   </si>
   <si>
-    <t>time</t>
-  </si>
-  <si>
     <t>owner</t>
   </si>
   <si>
@@ -81,6 +78,12 @@
   </si>
   <si>
     <t>מעבר על ליקויי אבטחה</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>end_time</t>
   </si>
 </sst>
 </file>
@@ -474,18 +477,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81840B73-A939-4138-9F05-60B93E3DBEB3}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" customWidth="1"/>
     <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" customWidth="1"/>
+    <col min="4" max="5" width="12.25" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,21 +499,24 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="3">
         <v>46131</v>
@@ -518,19 +524,22 @@
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C3" s="3">
         <v>46131</v>
@@ -538,19 +547,22 @@
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
+      <c r="E3" s="4">
+        <v>0.625</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C4" s="3">
         <v>46131</v>
@@ -558,11 +570,14 @@
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347EC3FB-1B72-4243-9EBD-6BA1BE9F0BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223AF55F-56C0-4557-8A0B-2C4E22A60E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223AF55F-56C0-4557-8A0B-2C4E22A60E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD4696D-7871-4271-8BE9-316D596A9DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="16">
   <si>
     <t>project_name</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81840B73-A939-4138-9F05-60B93E3DBEB3}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
@@ -577,6 +577,213 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46134</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46135</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46136</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD4696D-7871-4271-8BE9-316D596A9DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE3FFCE-AC65-49B5-A096-8A7AE32EE649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46133</v>
+        <v>46137</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
@@ -588,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D5" s="4">
         <v>0.41666666666666669</v>
@@ -611,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D6" s="4">
         <v>0.60416666666666663</v>
@@ -634,7 +634,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="D7" s="4">
         <v>0.64583333333333337</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D8" s="4">
         <v>0.41666666666666669</v>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D9" s="4">
         <v>0.60416666666666663</v>
@@ -703,7 +703,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="3">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="D10" s="4">
         <v>0.64583333333333337</v>
@@ -726,7 +726,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D11" s="4">
         <v>0.41666666666666669</v>
@@ -749,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D12" s="4">
         <v>0.60416666666666663</v>
@@ -772,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="D13" s="4">
         <v>0.64583333333333337</v>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE3FFCE-AC65-49B5-A096-8A7AE32EE649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E9F3DD-270D-4728-A7CF-AC657EFD6770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
@@ -588,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="D5" s="4">
         <v>0.41666666666666669</v>
@@ -611,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="3">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="D6" s="4">
         <v>0.60416666666666663</v>
@@ -634,7 +634,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="D7" s="4">
         <v>0.64583333333333337</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="D8" s="4">
         <v>0.41666666666666669</v>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="D9" s="4">
         <v>0.60416666666666663</v>
@@ -703,7 +703,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="3">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="D10" s="4">
         <v>0.64583333333333337</v>
@@ -726,7 +726,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>46140</v>
+        <v>46145</v>
       </c>
       <c r="D11" s="4">
         <v>0.41666666666666669</v>
@@ -749,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>46140</v>
+        <v>46145</v>
       </c>
       <c r="D12" s="4">
         <v>0.60416666666666663</v>
@@ -772,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>46140</v>
+        <v>46145</v>
       </c>
       <c r="D13" s="4">
         <v>0.64583333333333337</v>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E9F3DD-270D-4728-A7CF-AC657EFD6770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D61608-2953-4959-9D91-E8EB43075697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="18">
   <si>
     <t>project_name</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>end_time</t>
+  </si>
+  <si>
+    <t>אלטשולר - סטטוס צוותי</t>
+  </si>
+  <si>
+    <t>צוות אלטשולר</t>
   </si>
 </sst>
 </file>
@@ -480,7 +486,7 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="16.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" customWidth="1"/>
     <col min="3" max="3" width="18.1640625" customWidth="1"/>
     <col min="4" max="5" width="12.25" customWidth="1"/>
@@ -519,7 +525,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -542,7 +548,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -565,7 +571,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
@@ -580,15 +586,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="28" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="D5" s="4">
         <v>0.41666666666666669</v>
@@ -597,7 +603,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>7</v>
@@ -611,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="3">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="D6" s="4">
         <v>0.60416666666666663</v>
@@ -634,7 +640,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="D7" s="4">
         <v>0.64583333333333337</v>
@@ -657,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="D8" s="4">
         <v>0.41666666666666669</v>
@@ -674,22 +680,22 @@
     </row>
     <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="D9" s="4">
-        <v>0.60416666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E9" s="4">
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>7</v>
@@ -703,7 +709,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="3">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="D10" s="4">
         <v>0.64583333333333337</v>
@@ -726,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="D11" s="4">
         <v>0.41666666666666669</v>
@@ -749,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="D12" s="4">
         <v>0.60416666666666663</v>
@@ -764,24 +770,24 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="28" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="D13" s="4">
-        <v>0.64583333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E13" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>7</v>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D61608-2953-4959-9D91-E8EB43075697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DA308A-5D75-4177-B697-FE28FD7F3B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="18">
   <si>
     <t>project_name</t>
   </si>
@@ -483,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81840B73-A939-4138-9F05-60B93E3DBEB3}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="8.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.08203125" bestFit="1" customWidth="1"/>
@@ -525,7 +525,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="D2" s="4">
         <v>0.41666666666666669</v>
@@ -548,7 +548,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="D3" s="4">
         <v>0.60416666666666663</v>
@@ -571,7 +571,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="D4" s="4">
         <v>0.64583333333333337</v>
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="D5" s="4">
         <v>0.41666666666666669</v>
@@ -617,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="3">
-        <v>46145</v>
+        <v>46149</v>
       </c>
       <c r="D6" s="4">
         <v>0.60416666666666663</v>
@@ -640,7 +640,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>46145</v>
+        <v>46149</v>
       </c>
       <c r="D7" s="4">
         <v>0.64583333333333337</v>
@@ -663,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>46145</v>
+        <v>46149</v>
       </c>
       <c r="D8" s="4">
         <v>0.41666666666666669</v>
@@ -686,7 +686,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <v>46145</v>
+        <v>46149</v>
       </c>
       <c r="D9" s="4">
         <v>0.41666666666666669</v>
@@ -709,7 +709,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D10" s="4">
         <v>0.64583333333333337</v>
@@ -732,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D11" s="4">
         <v>0.41666666666666669</v>
@@ -755,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D12" s="4">
         <v>0.60416666666666663</v>
@@ -778,7 +778,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D13" s="4">
         <v>0.41666666666666669</v>
@@ -790,6 +790,98 @@
         <v>17</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46151</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46151</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46151</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46151</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DA308A-5D75-4177-B697-FE28FD7F3B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B032462-DF3D-40FB-B00C-4886B25052A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -597,10 +597,10 @@
         <v>46148</v>
       </c>
       <c r="D5" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E5" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>17</v>
@@ -689,10 +689,10 @@
         <v>46149</v>
       </c>
       <c r="D9" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E9" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>17</v>
@@ -781,10 +781,10 @@
         <v>46150</v>
       </c>
       <c r="D13" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E13" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>17</v>
@@ -873,10 +873,10 @@
         <v>46151</v>
       </c>
       <c r="D17" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E17" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>17</v>

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B032462-DF3D-40FB-B00C-4886B25052A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE394A4-7AFC-47C1-881F-31D1C1E67C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{654D42B8-71DE-4F6E-86CF-583F17BFBCF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
   <si>
     <t>project_name</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>צוות אלטשולר</t>
+  </si>
+  <si>
+    <t>סטטוס צוות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סטטוס שבועי צוות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">סטטוס צוות </t>
   </si>
 </sst>
 </file>
@@ -591,7 +600,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <v>46148</v>
@@ -683,7 +692,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>46149</v>
@@ -775,7 +784,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>46150</v>
@@ -867,7 +876,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <v>46151</v>
